--- a/exemplos/devolutiva_exemplo.xlsx
+++ b/exemplos/devolutiva_exemplo.xlsx
@@ -14,33 +14,54 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Nota Fiscal</t>
   </si>
   <si>
-    <t>Data Viagem</t>
+    <t>Veículo</t>
   </si>
   <si>
     <t>Custo Viagem</t>
   </si>
   <si>
+    <t>1000001</t>
+  </si>
+  <si>
     <t>1000002-1</t>
   </si>
   <si>
-    <t>001000003, 001000004</t>
-  </si>
-  <si>
-    <t>1000011-00</t>
+    <t>1000003</t>
+  </si>
+  <si>
+    <t>1000006</t>
+  </si>
+  <si>
+    <t>1000007</t>
+  </si>
+  <si>
+    <t>1000008</t>
+  </si>
+  <si>
+    <t>1000099</t>
+  </si>
+  <si>
+    <t>ABC1D23</t>
+  </si>
+  <si>
+    <t>XYZ9K88</t>
+  </si>
+  <si>
+    <t>DEF4567</t>
+  </si>
+  <si>
+    <t>ZZZ0Z00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -70,9 +91,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,80 +402,80 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1000001</v>
-      </c>
-      <c r="B2" s="1">
-        <v>46282</v>
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
-        <v>46283</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>980.5</v>
+        <v>980</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
-        <v>46284</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>2300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
-        <v>46295</v>
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>2000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6">
-        <v>1000013</v>
-      </c>
-      <c r="B6" s="1">
-        <v>46290</v>
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>1300</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7">
-        <v>2000001</v>
-      </c>
-      <c r="B7" s="1">
-        <v>46285</v>
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8">
-        <v>2000002</v>
-      </c>
-      <c r="B8" s="1">
-        <v>46286</v>
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>640</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
